--- a/tabtools/qa/baseline/workbooks/table1_tc_forced_types.xlsx
+++ b/tabtools/qa/baseline/workbooks/table1_tc_forced_types.xlsx
@@ -1318,7 +1318,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="207">
+  <borders count="209">
     <border>
       <left/>
       <right/>
@@ -1332,6 +1332,8 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -2736,7 +2738,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -2744,803 +2746,805 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="155" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="157" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="159" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="175" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="177" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="179" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="197" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="199" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="213" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="219" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="175" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="179" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="269" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="271" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="273" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="275" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="277" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3557,212 +3561,213 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="3" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" style="4" customWidth="true"/>
-    <col min="3" max="4" width="14.7109375" style="5" customWidth="true"/>
-    <col min="5" max="5" width="10.7109375" style="6" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="4" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="5" customWidth="true"/>
+    <col min="4" max="4" width="17.7109375" style="6" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="8" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="177" t="s">
+      <c r="C1" s="179" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="178" t="s">
+      <c r="D1" s="180" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="179" t="s">
+      <c r="E1" s="181" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="true" ht="30" customHeight="true">
-      <c r="A2" s="120" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="122" t="s">
+      <c r="C2" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="123" t="s">
+      <c r="D2" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="124" t="s">
+      <c r="E2" s="126" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="125" t="s">
+      <c r="A3" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="127" t="s">
+      <c r="C3" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="128" t="s">
+      <c r="D3" s="130" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="129" t="s">
+      <c r="E3" s="131" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="s">
+      <c r="A4" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="180" t="s">
+      <c r="C4" s="182" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="181" t="s">
+      <c r="D4" s="183" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="182" t="s">
+      <c r="E4" s="184" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="136" t="s">
+      <c r="B5" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="183" t="s">
+      <c r="C5" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="184" t="s">
+      <c r="D5" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="185" t="s">
+      <c r="E5" s="187" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="140" t="s">
+      <c r="A6" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="141" t="s">
+      <c r="B6" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="186" t="s">
+      <c r="C6" s="188" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="187" t="s">
+      <c r="D6" s="189" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="188" t="s">
+      <c r="E6" s="190" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="146" t="s">
+      <c r="B7" s="148" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="189" t="s">
+      <c r="C7" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="190" t="s">
+      <c r="D7" s="192" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="191" t="s">
+      <c r="E7" s="193" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="151" t="s">
+      <c r="B8" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="192" t="s">
+      <c r="C8" s="194" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="193" t="s">
+      <c r="D8" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="194" t="s">
+      <c r="E8" s="196" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="155" t="s">
+      <c r="A9" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="156" t="s">
+      <c r="B9" s="158" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="195" t="s">
+      <c r="C9" s="197" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="196" t="s">
+      <c r="D9" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="197" t="s">
+      <c r="E9" s="199" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="160" t="s">
+      <c r="A10" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="161" t="s">
+      <c r="B10" s="163" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="198" t="s">
+      <c r="C10" s="200" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="199" t="s">
+      <c r="D10" s="201" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="200" t="s">
+      <c r="E10" s="202" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="165" t="s">
+      <c r="A11" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="166" t="s">
+      <c r="B11" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="201" t="s">
+      <c r="C11" s="203" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="202" t="s">
+      <c r="D11" s="204" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="203" t="s">
+      <c r="E11" s="205" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="170" t="s">
+      <c r="A12" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="173" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="204" t="s">
+      <c r="C12" s="206" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="205" t="s">
+      <c r="D12" s="207" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="206" t="s">
+      <c r="E12" s="208" t="s">
         <v>1</v>
       </c>
     </row>
